--- a/demos/test1.xlsx
+++ b/demos/test1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t xml:space="preserve">Produkt</t>
   </si>
@@ -175,13 +175,10 @@
     <t xml:space="preserve">CPU</t>
   </si>
   <si>
-    <t xml:space="preserve">Ryzen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i7</t>
+    <t xml:space="preserve">Ryzen 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core i7</t>
   </si>
   <si>
     <t xml:space="preserve">GPU</t>
@@ -193,46 +190,28 @@
     <t xml:space="preserve">RX</t>
   </si>
   <si>
-    <t xml:space="preserve">XT</t>
-  </si>
-  <si>
     <t xml:space="preserve">RAM</t>
   </si>
   <si>
     <t xml:space="preserve">DDR4</t>
   </si>
   <si>
-    <t xml:space="preserve">16GB</t>
-  </si>
-  <si>
     <t xml:space="preserve">DDR5</t>
   </si>
   <si>
-    <t xml:space="preserve">32GB</t>
-  </si>
-  <si>
     <t xml:space="preserve">SSD</t>
   </si>
   <si>
     <t xml:space="preserve">NVMe</t>
   </si>
   <si>
-    <t xml:space="preserve">1TB</t>
-  </si>
-  <si>
     <t xml:space="preserve">SATA</t>
   </si>
   <si>
-    <t xml:space="preserve">2TB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mainboard</t>
   </si>
   <si>
     <t xml:space="preserve">AM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board</t>
   </si>
   <si>
     <t xml:space="preserve">LGA1700</t>
@@ -250,6 +229,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -309,8 +289,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -334,37 +318,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -437,1645 +421,1606 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ11"/>
+  <dimension ref="A1:CH11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AC1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" s="0" t="s">
+      <c r="AH1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="0" t="s">
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" s="0" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="0" t="s">
+      <c r="AK1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" s="0" t="s">
+      <c r="AL1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AN1" s="0" t="s">
+      <c r="AM1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AO1" s="0" t="s">
+      <c r="AN1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AP1" s="0" t="s">
+      <c r="AO1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AQ1" s="0" t="s">
+      <c r="AP1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AR1" s="0" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AS1" s="0" t="s">
+      <c r="AR1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AT1" s="0" t="s">
+      <c r="AS1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AU1" s="0" t="s">
+      <c r="AT1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AV1" s="0" t="s">
+      <c r="AU1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AW1" s="0" t="s">
+      <c r="AV1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AX1" s="0" t="s">
+      <c r="AW1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AY1" s="0" t="s">
+      <c r="AX1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AZ1" s="0" t="s">
+      <c r="AY1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="0" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>249</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>259</v>
-      </c>
-      <c r="F2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>199</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>265</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>205</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>275</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>215</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>220</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>285</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="Q2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>290</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="P2" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="S2" s="0" t="n">
+      <c r="Q2" s="1" t="n">
         <v>295</v>
       </c>
-      <c r="T2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>235</v>
       </c>
-      <c r="U2" s="0" t="n">
+      <c r="S2" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="T2" s="1" t="n">
         <v>240</v>
       </c>
-      <c r="W2" s="0" t="n">
+      <c r="U2" s="1" t="n">
         <v>310</v>
       </c>
-      <c r="X2" s="0" t="n">
+      <c r="V2" s="1" t="n">
         <v>245</v>
       </c>
-      <c r="Y2" s="0" t="n">
+      <c r="W2" s="1" t="n">
         <v>315</v>
       </c>
-      <c r="Z2" s="0" t="n">
+      <c r="X2" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="AA2" s="0" t="n">
+      <c r="Y2" s="1" t="n">
         <v>320</v>
       </c>
-      <c r="AB2" s="0" t="n">
+      <c r="Z2" s="1" t="n">
         <v>255</v>
       </c>
-      <c r="AC2" s="0" t="n">
+      <c r="AA2" s="1" t="n">
         <v>330</v>
       </c>
-      <c r="AD2" s="0" t="n">
+      <c r="AB2" s="1" t="n">
         <v>260</v>
       </c>
-      <c r="AE2" s="0" t="n">
+      <c r="AC2" s="1" t="n">
         <v>335</v>
       </c>
-      <c r="AF2" s="0" t="n">
+      <c r="AD2" s="1" t="n">
         <v>265</v>
       </c>
-      <c r="AG2" s="0" t="n">
+      <c r="AE2" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="AH2" s="0" t="n">
+      <c r="AF2" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="AI2" s="0" t="n">
+      <c r="AG2" s="1" t="n">
         <v>345</v>
       </c>
-      <c r="AJ2" s="0" t="n">
+      <c r="AH2" s="1" t="n">
         <v>275</v>
       </c>
-      <c r="AK2" s="0" t="n">
+      <c r="AI2" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="AL2" s="0" t="n">
+      <c r="AJ2" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="AM2" s="0" t="n">
+      <c r="AK2" s="1" t="n">
         <v>355</v>
       </c>
-      <c r="AN2" s="0" t="n">
+      <c r="AL2" s="1" t="n">
         <v>285</v>
       </c>
-      <c r="AO2" s="0" t="n">
+      <c r="AM2" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="AP2" s="0" t="n">
+      <c r="AN2" s="1" t="n">
         <v>290</v>
       </c>
-      <c r="AQ2" s="0" t="n">
+      <c r="AO2" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="AR2" s="0" t="n">
+      <c r="AP2" s="1" t="n">
         <v>295</v>
       </c>
-      <c r="AS2" s="0" t="n">
+      <c r="AQ2" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="AT2" s="0" t="n">
+      <c r="AR2" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="AU2" s="0" t="n">
+      <c r="AS2" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="AV2" s="0" t="n">
+      <c r="AT2" s="1" t="n">
         <v>305</v>
       </c>
-      <c r="AW2" s="0" t="n">
+      <c r="AU2" s="1" t="n">
         <v>310</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>329</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>339</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>289</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>345</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>295</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>355</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>305</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>310</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>315</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="P3" s="1" t="n">
         <v>320</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="Q3" s="1" t="n">
         <v>375</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>325</v>
       </c>
-      <c r="U3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="T3" s="1" t="n">
         <v>330</v>
       </c>
-      <c r="W3" s="0" t="n">
+      <c r="U3" s="1" t="n">
         <v>390</v>
       </c>
-      <c r="X3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <v>335</v>
       </c>
-      <c r="Y3" s="0" t="n">
+      <c r="W3" s="1" t="n">
         <v>395</v>
       </c>
-      <c r="Z3" s="0" t="n">
+      <c r="X3" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="AA3" s="0" t="n">
+      <c r="Y3" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="AB3" s="0" t="n">
+      <c r="Z3" s="1" t="n">
         <v>345</v>
       </c>
-      <c r="AC3" s="0" t="n">
+      <c r="AA3" s="1" t="n">
         <v>410</v>
       </c>
-      <c r="AD3" s="0" t="n">
+      <c r="AB3" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="AE3" s="0" t="n">
+      <c r="AC3" s="1" t="n">
         <v>415</v>
       </c>
-      <c r="AF3" s="0" t="n">
+      <c r="AD3" s="1" t="n">
         <v>355</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AE3" s="1" t="n">
         <v>420</v>
       </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AF3" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="AI3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>425</v>
       </c>
-      <c r="AJ3" s="0" t="n">
+      <c r="AH3" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="AK3" s="0" t="n">
+      <c r="AI3" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="AL3" s="0" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="AM3" s="0" t="n">
+      <c r="AK3" s="1" t="n">
         <v>435</v>
       </c>
-      <c r="AN3" s="0" t="n">
+      <c r="AL3" s="1" t="n">
         <v>375</v>
       </c>
-      <c r="AO3" s="0" t="n">
+      <c r="AM3" s="1" t="n">
         <v>440</v>
       </c>
-      <c r="AP3" s="0" t="n">
+      <c r="AN3" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="AQ3" s="0" t="n">
+      <c r="AO3" s="1" t="n">
         <v>445</v>
       </c>
-      <c r="AR3" s="0" t="n">
+      <c r="AP3" s="1" t="n">
         <v>385</v>
       </c>
-      <c r="AS3" s="0" t="n">
+      <c r="AQ3" s="1" t="n">
         <v>450</v>
       </c>
-      <c r="AT3" s="0" t="n">
+      <c r="AR3" s="1" t="n">
         <v>390</v>
       </c>
-      <c r="AU3" s="0" t="n">
+      <c r="AS3" s="1" t="n">
         <v>460</v>
       </c>
-      <c r="AV3" s="0" t="n">
+      <c r="AT3" s="1" t="n">
         <v>395</v>
       </c>
-      <c r="AW3" s="0" t="n">
+      <c r="AU3" s="1" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>599</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>599</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>4060</v>
-      </c>
-      <c r="H4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>609</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>499</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>620</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>510</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>630</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>520</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>640</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>530</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>650</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="P4" s="1" t="n">
         <v>540</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="Q4" s="1" t="n">
         <v>660</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>550</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>670</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="T4" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="U4" s="1" t="n">
         <v>680</v>
       </c>
-      <c r="W4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>570</v>
       </c>
-      <c r="X4" s="0" t="n">
+      <c r="W4" s="1" t="n">
         <v>690</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="X4" s="1" t="n">
         <v>580</v>
       </c>
-      <c r="Z4" s="0" t="n">
+      <c r="Y4" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="AA4" s="0" t="n">
+      <c r="Z4" s="1" t="n">
         <v>590</v>
       </c>
-      <c r="AB4" s="0" t="n">
+      <c r="AA4" s="1" t="n">
         <v>710</v>
       </c>
-      <c r="AC4" s="0" t="n">
+      <c r="AB4" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="AD4" s="0" t="n">
+      <c r="AC4" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AD4" s="1" t="n">
         <v>610</v>
       </c>
-      <c r="AF4" s="0" t="n">
+      <c r="AE4" s="1" t="n">
         <v>730</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AF4" s="1" t="n">
         <v>620</v>
       </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>740</v>
       </c>
-      <c r="AI4" s="0" t="n">
+      <c r="AH4" s="1" t="n">
         <v>630</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AI4" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="AK4" s="0" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>640</v>
       </c>
-      <c r="AL4" s="0" t="n">
+      <c r="AK4" s="1" t="n">
         <v>760</v>
       </c>
-      <c r="AM4" s="0" t="n">
+      <c r="AL4" s="1" t="n">
         <v>650</v>
       </c>
-      <c r="AN4" s="0" t="n">
+      <c r="AM4" s="1" t="n">
         <v>770</v>
       </c>
-      <c r="AO4" s="0" t="n">
+      <c r="AN4" s="1" t="n">
         <v>660</v>
       </c>
-      <c r="AP4" s="0" t="n">
+      <c r="AO4" s="1" t="n">
         <v>780</v>
       </c>
-      <c r="AQ4" s="0" t="n">
+      <c r="AP4" s="1" t="n">
         <v>670</v>
       </c>
-      <c r="AR4" s="0" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>790</v>
       </c>
-      <c r="AS4" s="0" t="n">
+      <c r="AR4" s="1" t="n">
         <v>680</v>
       </c>
-      <c r="AT4" s="0" t="n">
+      <c r="AS4" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="AU4" s="0" t="n">
+      <c r="AT4" s="1" t="n">
         <v>690</v>
       </c>
-      <c r="AV4" s="0" t="n">
+      <c r="AU4" s="1" t="n">
         <v>810</v>
       </c>
-      <c r="AW4" s="0" t="n">
+      <c r="AV4" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="AX4" s="0" t="n">
+      <c r="AW4" s="1" t="n">
         <v>820</v>
       </c>
-      <c r="AY4" s="0" t="n">
+      <c r="AX4" s="1" t="n">
         <v>710</v>
       </c>
-      <c r="AZ4" s="0" t="n">
+      <c r="AY4" s="1" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="0" t="n">
+      <c r="A5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>899</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>7800</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>915</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>930</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>760</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>940</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>770</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>950</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>780</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>960</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>790</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>970</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <v>980</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>810</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>990</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>820</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="T5" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="AA5" s="0" t="n">
+      <c r="X5" s="1" t="n">
         <v>830</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="Y5" s="1" t="n">
         <v>1010</v>
       </c>
-      <c r="AF5" s="0" t="n">
+      <c r="AC5" s="1" t="n">
         <v>840</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AD5" s="1" t="n">
         <v>1020</v>
       </c>
-      <c r="AK5" s="0" t="n">
+      <c r="AH5" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="AL5" s="0" t="n">
+      <c r="AI5" s="1" t="n">
         <v>1030</v>
       </c>
-      <c r="AP5" s="0" t="n">
+      <c r="AM5" s="1" t="n">
         <v>860</v>
       </c>
-      <c r="AQ5" s="0" t="n">
+      <c r="AN5" s="1" t="n">
         <v>1040</v>
       </c>
-      <c r="AU5" s="0" t="n">
+      <c r="AR5" s="1" t="n">
         <v>870</v>
       </c>
-      <c r="AV5" s="0" t="n">
+      <c r="AS5" s="1" t="n">
         <v>1050</v>
       </c>
-      <c r="AZ5" s="0" t="n">
+      <c r="AW5" s="1" t="n">
         <v>880</v>
       </c>
-      <c r="BA5" s="0" t="n">
+      <c r="AX5" s="1" t="n">
         <v>1060</v>
       </c>
-      <c r="BE5" s="0" t="n">
+      <c r="BB5" s="1" t="n">
         <v>890</v>
       </c>
-      <c r="BF5" s="0" t="n">
+      <c r="BC5" s="1" t="n">
         <v>1070</v>
       </c>
-      <c r="BJ5" s="0" t="n">
+      <c r="BG5" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="BK5" s="0" t="n">
+      <c r="BH5" s="1" t="n">
         <v>1080</v>
       </c>
-      <c r="BO5" s="0" t="n">
+      <c r="BL5" s="1" t="n">
         <v>910</v>
       </c>
-      <c r="BP5" s="0" t="n">
+      <c r="BM5" s="1" t="n">
         <v>1090</v>
       </c>
-      <c r="BT5" s="0" t="n">
+      <c r="BQ5" s="1" t="n">
         <v>920</v>
       </c>
-      <c r="BU5" s="0" t="n">
+      <c r="BR5" s="1" t="n">
         <v>1100</v>
       </c>
-      <c r="BY5" s="0" t="n">
+      <c r="BV5" s="1" t="n">
         <v>930</v>
       </c>
-      <c r="BZ5" s="0" t="n">
+      <c r="BW5" s="1" t="n">
         <v>1110</v>
       </c>
-      <c r="CD5" s="0" t="n">
+      <c r="CA5" s="1" t="n">
         <v>940</v>
       </c>
-      <c r="CE5" s="0" t="n">
+      <c r="CB5" s="1" t="n">
         <v>1120</v>
       </c>
-      <c r="CI5" s="0" t="n">
+      <c r="CF5" s="1" t="n">
         <v>950</v>
       </c>
-      <c r="CJ5" s="0" t="n">
+      <c r="CG5" s="1" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="0" t="n">
+      <c r="A6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>72</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>74</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <v>57</v>
-      </c>
-      <c r="P6" s="0" t="n">
-        <v>76</v>
-      </c>
-      <c r="R6" s="0" t="n">
-        <v>59</v>
-      </c>
-      <c r="T6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="T6" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="X6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="Z6" s="0" t="n">
+      <c r="X6" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="Z6" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AB6" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="AF6" s="0" t="n">
+      <c r="AD6" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AF6" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="AJ6" s="0" t="n">
+      <c r="AH6" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="AL6" s="0" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="AN6" s="0" t="n">
+      <c r="AL6" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="AP6" s="0" t="n">
+      <c r="AN6" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="AR6" s="0" t="n">
+      <c r="AP6" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="AT6" s="0" t="n">
+      <c r="AR6" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="AV6" s="0" t="n">
+      <c r="AT6" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="AX6" s="0" t="n">
+      <c r="AV6" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="AZ6" s="0" t="n">
+      <c r="AX6" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="BB6" s="0" t="n">
+      <c r="AZ6" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="BD6" s="0" t="n">
+      <c r="BB6" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="BF6" s="0" t="n">
+      <c r="BD6" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="BH6" s="0" t="n">
+      <c r="BF6" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="BJ6" s="0" t="n">
+      <c r="BH6" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="BL6" s="0" t="n">
+      <c r="BJ6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="BM6" s="0" t="n">
+      <c r="BK6" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="BO6" s="0" t="n">
+      <c r="BM6" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="BP6" s="0" t="n">
+      <c r="BN6" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="BR6" s="0" t="n">
+      <c r="BP6" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="BS6" s="0" t="n">
+      <c r="BQ6" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="BU6" s="0" t="n">
+      <c r="BS6" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="BV6" s="0" t="n">
+      <c r="BT6" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="BX6" s="0" t="n">
+      <c r="BV6" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="BY6" s="0" t="n">
+      <c r="BW6" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="CA6" s="0" t="n">
+      <c r="BY6" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="CB6" s="0" t="n">
+      <c r="BZ6" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="CD6" s="0" t="n">
+      <c r="CB6" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="CE6" s="0" t="n">
+      <c r="CC6" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="CG6" s="0" t="n">
+      <c r="CE6" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="CH6" s="0" t="n">
+      <c r="CF6" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="CJ6" s="0" t="n">
+      <c r="CH6" s="1" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>119</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="P7" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="Q7" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="T7" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="U7" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="W7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="X7" s="0" t="n">
+      <c r="W7" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="X7" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="Z7" s="0" t="n">
+      <c r="Y7" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="AA7" s="0" t="n">
+      <c r="Z7" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="AA7" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="AC7" s="0" t="n">
+      <c r="AB7" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AC7" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AD7" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="AF7" s="0" t="n">
+      <c r="AE7" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AF7" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="AI7" s="0" t="n">
+      <c r="AH7" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="AJ7" s="0" t="n">
+      <c r="AI7" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="AK7" s="0" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="AL7" s="0" t="n">
+      <c r="AK7" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="AM7" s="0" t="n">
+      <c r="AL7" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="AN7" s="0" t="n">
+      <c r="AM7" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="AO7" s="0" t="n">
+      <c r="AN7" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="AP7" s="0" t="n">
+      <c r="AO7" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="AQ7" s="0" t="n">
+      <c r="AP7" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="AR7" s="0" t="n">
+      <c r="AQ7" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="AS7" s="0" t="n">
+      <c r="AR7" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="AT7" s="0" t="n">
+      <c r="AS7" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="AU7" s="0" t="n">
+      <c r="AT7" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="AV7" s="0" t="n">
+      <c r="AU7" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="AW7" s="0" t="n">
+      <c r="AV7" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="AX7" s="0" t="n">
+      <c r="AW7" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="AY7" s="0" t="n">
+      <c r="AX7" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="AZ7" s="0" t="n">
+      <c r="AY7" s="1" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="0" t="n">
+      <c r="A8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="C8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="Q8" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="U8" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="W8" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="X8" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="Z8" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AA8" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AC8" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="AF8" s="0" t="n">
+      <c r="AD8" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AF8" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="AG8" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="AK8" s="0" t="n">
+      <c r="AI8" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="AL8" s="0" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="AN8" s="0" t="n">
+      <c r="AL8" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="AO8" s="0" t="n">
+      <c r="AM8" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="AQ8" s="0" t="n">
+      <c r="AO8" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="AR8" s="0" t="n">
+      <c r="AP8" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="AT8" s="0" t="n">
+      <c r="AR8" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="AU8" s="0" t="n">
+      <c r="AS8" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AU8" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="AX8" s="0" t="n">
+      <c r="AV8" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="AZ8" s="0" t="n">
+      <c r="AX8" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="BA8" s="0" t="n">
+      <c r="AY8" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="BB8" s="0" t="n">
+      <c r="AZ8" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="BC8" s="0" t="n">
+      <c r="BA8" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="BD8" s="0" t="n">
+      <c r="BB8" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="BE8" s="0" t="n">
+      <c r="BC8" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="BF8" s="0" t="n">
+      <c r="BD8" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="BG8" s="0" t="n">
+      <c r="BE8" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="BH8" s="0" t="n">
+      <c r="BF8" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="BI8" s="0" t="n">
+      <c r="BG8" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="BJ8" s="0" t="n">
+      <c r="BH8" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="BK8" s="0" t="n">
+      <c r="BI8" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="BL8" s="0" t="n">
+      <c r="BJ8" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="BM8" s="0" t="n">
+      <c r="BK8" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="BN8" s="0" t="n">
+      <c r="BL8" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="BO8" s="0" t="n">
+      <c r="BM8" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="BP8" s="0" t="n">
+      <c r="BN8" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="BQ8" s="0" t="n">
+      <c r="BO8" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="BR8" s="0" t="n">
+      <c r="BP8" s="1" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="0" t="n">
+      <c r="A9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="0" t="n">
+      <c r="C9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="P9" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="Q9" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="R9" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="T9" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="U9" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="W9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="X9" s="0" t="n">
+      <c r="W9" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="Y9" s="0" t="n">
+      <c r="X9" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="Z9" s="0" t="n">
+      <c r="Y9" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="AA9" s="0" t="n">
+      <c r="Z9" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="AB9" s="0" t="n">
+      <c r="AA9" s="1" t="n">
         <v>176</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AB9" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AC9" s="1" t="n">
         <v>178</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AD9" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="AF9" s="0" t="n">
+      <c r="AE9" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="AG9" s="0" t="n">
+      <c r="AF9" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
         <v>182</v>
       </c>
-      <c r="AI9" s="0" t="n">
+      <c r="AH9" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="AJ9" s="0" t="n">
+      <c r="AI9" s="1" t="n">
         <v>184</v>
       </c>
-      <c r="AK9" s="0" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="AL9" s="0" t="n">
+      <c r="AK9" s="1" t="n">
         <v>186</v>
       </c>
-      <c r="AM9" s="0" t="n">
+      <c r="AL9" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="AN9" s="0" t="n">
+      <c r="AM9" s="1" t="n">
         <v>188</v>
       </c>
-      <c r="AO9" s="0" t="n">
+      <c r="AN9" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="AP9" s="0" t="n">
+      <c r="AO9" s="1" t="n">
         <v>190</v>
       </c>
-      <c r="AQ9" s="0" t="n">
+      <c r="AP9" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="AR9" s="0" t="n">
+      <c r="AQ9" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="AS9" s="0" t="n">
+      <c r="AR9" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="AT9" s="0" t="n">
+      <c r="AS9" s="1" t="n">
         <v>194</v>
       </c>
-      <c r="AU9" s="0" t="n">
+      <c r="AT9" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="AV9" s="0" t="n">
+      <c r="AU9" s="1" t="n">
         <v>196</v>
       </c>
-      <c r="AW9" s="0" t="n">
+      <c r="AV9" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="AX9" s="0" t="n">
+      <c r="AW9" s="1" t="n">
         <v>198</v>
       </c>
-      <c r="AY9" s="0" t="n">
+      <c r="AX9" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="AZ9" s="0" t="n">
+      <c r="AY9" s="1" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="A10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="0" t="n">
+      <c r="C10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="P10" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="T10" s="0" t="n">
+      <c r="Q10" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="U10" s="0" t="n">
+      <c r="R10" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="S10" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="W10" s="0" t="n">
+      <c r="T10" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="X10" s="0" t="n">
+      <c r="U10" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="Y10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="Z10" s="0" t="n">
+      <c r="W10" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="AA10" s="0" t="n">
+      <c r="X10" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="AB10" s="0" t="n">
+      <c r="Y10" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="AC10" s="0" t="n">
+      <c r="Z10" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AA10" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AB10" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="AF10" s="0" t="n">
+      <c r="AC10" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="AG10" s="0" t="n">
+      <c r="AD10" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="AH10" s="0" t="n">
+      <c r="AE10" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="AI10" s="0" t="n">
+      <c r="AF10" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AG10" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="AK10" s="0" t="n">
+      <c r="AH10" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="AL10" s="0" t="n">
+      <c r="AI10" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="AM10" s="0" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>176</v>
       </c>
-      <c r="AN10" s="0" t="n">
+      <c r="AK10" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="AO10" s="0" t="n">
+      <c r="AL10" s="1" t="n">
         <v>178</v>
       </c>
-      <c r="AP10" s="0" t="n">
+      <c r="AM10" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="AQ10" s="0" t="n">
+      <c r="AN10" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="AR10" s="0" t="n">
+      <c r="AO10" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="AS10" s="0" t="n">
+      <c r="AP10" s="1" t="n">
         <v>182</v>
       </c>
-      <c r="AT10" s="0" t="n">
+      <c r="AQ10" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="AU10" s="0" t="n">
+      <c r="AR10" s="1" t="n">
         <v>184</v>
       </c>
-      <c r="AV10" s="0" t="n">
+      <c r="AS10" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="AW10" s="0" t="n">
+      <c r="AT10" s="1" t="n">
         <v>186</v>
       </c>
-      <c r="AX10" s="0" t="n">
+      <c r="AU10" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="AY10" s="0" t="n">
+      <c r="AV10" s="1" t="n">
         <v>188</v>
       </c>
-      <c r="AZ10" s="0" t="n">
+      <c r="AW10" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="BA10" s="0" t="n">
+      <c r="AX10" s="1" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="A11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="P11" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="T11" s="0" t="n">
+      <c r="Q11" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="U11" s="0" t="n">
+      <c r="R11" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="S11" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="W11" s="0" t="n">
+      <c r="T11" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="X11" s="0" t="n">
+      <c r="U11" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="Y11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="Z11" s="0" t="n">
+      <c r="W11" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="AA11" s="0" t="n">
+      <c r="X11" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="AB11" s="0" t="n">
+      <c r="Y11" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="Z11" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AA11" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AB11" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="AF11" s="0" t="n">
+      <c r="AC11" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="AG11" s="0" t="n">
+      <c r="AD11" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="AH11" s="0" t="n">
+      <c r="AE11" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="AI11" s="0" t="n">
+      <c r="AF11" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="AJ11" s="0" t="n">
+      <c r="AG11" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="AK11" s="0" t="n">
+      <c r="AH11" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="AL11" s="0" t="n">
+      <c r="AI11" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="AM11" s="0" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="AN11" s="0" t="n">
+      <c r="AK11" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="AO11" s="0" t="n">
+      <c r="AL11" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="AP11" s="0" t="n">
+      <c r="AM11" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="AQ11" s="0" t="n">
+      <c r="AN11" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="AR11" s="0" t="n">
+      <c r="AO11" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="AS11" s="0" t="n">
+      <c r="AP11" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="AT11" s="0" t="n">
+      <c r="AQ11" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="AU11" s="0" t="n">
+      <c r="AR11" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="AV11" s="0" t="n">
+      <c r="AS11" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="AW11" s="0" t="n">
+      <c r="AT11" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="AX11" s="0" t="n">
+      <c r="AU11" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="AY11" s="0" t="n">
+      <c r="AV11" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="AZ11" s="0" t="n">
+      <c r="AW11" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="BA11" s="0" t="n">
+      <c r="AX11" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="BB11" s="0" t="n">
+      <c r="AY11" s="1" t="n">
         <v>105</v>
       </c>
     </row>
